--- a/tools/myCustomBlockly/製作積木教學/產生積木程式碼_TM1637.xlsx
+++ b/tools/myCustomBlockly/製作積木教學/產生積木程式碼_TM1637.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMANI\Desktop\自訂積木\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ArduinoSample\tools\myCustomBlockly\製作積木教學\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9132" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9135" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="變數" sheetId="5" r:id="rId1"/>
@@ -1159,8 +1159,20 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>''</t>
+    <t>'.showNumberDecEx('</t>
+  </si>
+  <si>
+    <t>value_num1</t>
+  </si>
+  <si>
+    <t>', 0x40, true, 2, 0); \n'</t>
+  </si>
+  <si>
+    <t>value_num2</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
     </r>
     <r>
       <rPr>
@@ -1305,7 +1317,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>,  0, false,  2, 2);</t>
+      <t>,  0, true,  2, 2);</t>
     </r>
     <r>
       <rPr>
@@ -1316,21 +1328,11 @@
       </rPr>
       <t xml:space="preserve"> \n '</t>
     </r>
-  </si>
-  <si>
-    <t>'.showNumberDecEx('</t>
-  </si>
-  <si>
-    <t>value_num1</t>
-  </si>
-  <si>
-    <t>', 0x40, true, 2, 0); \n'</t>
-  </si>
-  <si>
-    <t>value_num2</t>
-  </si>
-  <si>
-    <t>',  0, false,  2, 2); \n '</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>,  0, true,  2, 2); \n '</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1507,7 +1509,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1560,6 +1562,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1844,7 +1852,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
   </cols>
@@ -1879,12 +1887,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="62.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="32.77734375" customWidth="1"/>
+    <col min="1" max="1" width="62.75" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="10.125" customWidth="1"/>
+    <col min="4" max="4" width="32.75" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2025,12 +2033,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="64.5546875" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="4" max="4" width="32.88671875" customWidth="1"/>
-    <col min="5" max="5" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="64.5" customWidth="1"/>
+    <col min="2" max="2" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="32.875" customWidth="1"/>
+    <col min="5" max="5" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2185,9 +2193,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="69.5546875" customWidth="1"/>
+    <col min="1" max="1" width="69.5" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
@@ -2308,9 +2316,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="69.5546875" customWidth="1"/>
+    <col min="1" max="1" width="69.5" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
@@ -2420,9 +2428,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="69.5546875" customWidth="1"/>
+    <col min="1" max="1" width="69.5" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
@@ -2436,7 +2444,7 @@
       </c>
       <c r="D1" s="9" t="str">
         <f>"var code ="&amp;D3&amp;D5&amp;";"</f>
-        <v>var code =''tm_display'+value_clk+ value_dio+'.showNumberDecEx('+value_num1+', 0x40, true, 2, 0); \n'++''tm_display'+value_clk +value_dio+'.showNumberDecEx('+value_num2+',  0, false,  2, 2); \n '++;</v>
+        <v>var code =''tm_display'+value_clk+ value_dio+'.showNumberDecEx('+value_num1+', 0x40, true, 2, 0); \n'++''tm_display'+value_clk +value_dio+'.showNumberDecEx('+value_num2+,  0, true,  2, 2); \n '++;</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2453,13 +2461,13 @@
         <v>19</v>
       </c>
       <c r="G2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
         <v>42</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>43</v>
-      </c>
-      <c r="I2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2470,8 +2478,8 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="C4" s="17" t="s">
-        <v>41</v>
+      <c r="C4" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>22</v>
@@ -2483,12 +2491,12 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="19" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2496,7 +2504,7 @@
       <c r="C5" s="11"/>
       <c r="D5" s="14" t="str">
         <f>D4&amp;"+"&amp;E4&amp;"+"&amp;F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4&amp;"+"&amp;J4&amp;"+"&amp;K4</f>
-        <v>''tm_display'+value_clk +value_dio+'.showNumberDecEx('+value_num2+',  0, false,  2, 2); \n '++</v>
+        <v>''tm_display'+value_clk +value_dio+'.showNumberDecEx('+value_num2+,  0, true,  2, 2); \n '++</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2555,9 +2563,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="64.21875" customWidth="1"/>
+    <col min="1" max="1" width="64.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
